--- a/authorization_forms/024_recurring_credit_card_authorization_form--authorization_forms.xlsx
+++ b/authorization_forms/024_recurring_credit_card_authorization_form--authorization_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C77"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1500,68 +1500,68 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>expiration_year_choices</t>
+          <t>start_month_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>january</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>January</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>expiration_year_choices</t>
+          <t>start_month_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>february</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>February</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>expiration_year_choices</t>
+          <t>start_month_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>march</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>March</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>expiration_year_choices</t>
+          <t>start_month_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>april</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>April</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>january</t>
+          <t>may</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>May</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>february</t>
+          <t>june</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>June</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>march</t>
+          <t>july</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>March</t>
+          <t>July</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>april</t>
+          <t>august</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>August</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>may</t>
+          <t>september</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>September</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>june</t>
+          <t>october</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>October</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>july</t>
+          <t>november</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>November</t>
         </is>
       </c>
     </row>
@@ -1692,80 +1692,80 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>august</t>
+          <t>december</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>December</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>start_month_choices</t>
+          <t>start_year_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>september</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>September</t>
+          <t>2015</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>start_month_choices</t>
+          <t>start_year_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>october</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>October</t>
+          <t>2016</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>start_month_choices</t>
+          <t>start_year_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>november</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>2017</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>start_month_choices</t>
+          <t>start_year_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>december</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>December</t>
+          <t>2018</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2019</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2020</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
@@ -1828,250 +1828,250 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2022</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>start_year_choices</t>
+          <t>frequency_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>start_year_choices</t>
+          <t>frequency_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>start_year_choices</t>
+          <t>frequency_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>start_year_choices</t>
+          <t>frequency_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>one-time</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>One-time</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>frequency_choices</t>
+          <t>authorization_type_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>recurring_payment</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Recurring Payment</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>frequency_choices</t>
+          <t>authorization_type_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>one-time_payment</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>One-time Payment</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>frequency_choices</t>
+          <t>payment_type_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>annually</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Annually</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>frequency_choices</t>
+          <t>payment_type_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>one-time</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>One-time</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>authorization_type_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>recurring_payment</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Recurring Payment</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>authorization_type_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>one-time_payment</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>One-time Payment</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>payment_type_choices</t>
+          <t>card_expiration_month_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>january</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>January</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>payment_type_choices</t>
+          <t>card_expiration_month_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>february</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>February</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>card_expiration_month_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>march</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>March</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>card_expiration_month_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>april</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>April</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>january</t>
+          <t>may</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>May</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>february</t>
+          <t>june</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>June</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>march</t>
+          <t>july</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>March</t>
+          <t>July</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>april</t>
+          <t>august</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>August</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>may</t>
+          <t>september</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>September</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>june</t>
+          <t>october</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>October</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>july</t>
+          <t>november</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>November</t>
         </is>
       </c>
     </row>
@@ -2202,80 +2202,80 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>august</t>
+          <t>december</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>December</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>card_expiration_month_choices</t>
+          <t>card_expiration_year_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>september</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>September</t>
+          <t>2015</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>card_expiration_month_choices</t>
+          <t>card_expiration_year_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>october</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>October</t>
+          <t>2016</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>card_expiration_month_choices</t>
+          <t>card_expiration_year_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>november</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>2017</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>card_expiration_month_choices</t>
+          <t>card_expiration_year_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>december</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>December</t>
+          <t>2018</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2019</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2020</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
@@ -2338,78 +2338,10 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>card_expiration_year_choices</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>card_expiration_year_choices</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>card_expiration_year_choices</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>card_expiration_year_choices</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
